--- a/ejemplos/Importar-incompletos.xlsx
+++ b/ejemplos/Importar-incompletos.xlsx
@@ -457,7 +457,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Código externo</t>
+          <t>Código proveedor</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">

--- a/ejemplos/Importar-incompletos.xlsx
+++ b/ejemplos/Importar-incompletos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1124,22 +1124,24 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>1001000</v>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>1001293</t>
+        </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Dana Transmisiones</t>
+          <t>Hella Iluminación</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No GS1</t>
+          <t>GS1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>PROP-C-200</t>
+          <t>07500001234563</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1163,37 +1165,75 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
+        <v>1001000</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dana Transmisiones</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>No GS1</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>PROP-C-200</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Unidad</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
         <v>1023711</v>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Delphi Technologies</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>No GS1</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>PROP-C-200</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Presentación</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Pallet</t>
         </is>
       </c>
-      <c r="G20" t="n">
+      <c r="G21" t="n">
         <v>96</v>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
